--- a/Output Data Tables/APAT Outputs/Aircraft Operating Costs Tables/2025/Crew_Costs_by_Aircraft_and_Airline_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aircraft Operating Costs Tables/2025/Crew_Costs_by_Aircraft_and_Airline_2025.xlsx
@@ -13,11 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="69" uniqueCount="69">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E135</t>
+  </si>
+  <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,7 +36,10 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -63,9 +72,24 @@
     <t>A321NEO</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
   </si>
   <si>
+    <t>B737-300</t>
+  </si>
+  <si>
+    <t>B737-400</t>
+  </si>
+  <si>
+    <t>B737-500</t>
+  </si>
+  <si>
     <t>B737-700</t>
   </si>
   <si>
@@ -133,6 +157,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Breeze</t>
@@ -238,33 +265,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="10.140625" customWidth="true"/>
     <col min="3" max="3" width="10.140625" customWidth="true"/>
     <col min="4" max="4" width="11.140625" customWidth="true"/>
-    <col min="5" max="5" width="10.140625" customWidth="true"/>
-    <col min="6" max="6" width="11.140625" customWidth="true"/>
-    <col min="7" max="7" width="10.140625" customWidth="true"/>
+    <col min="5" max="5" width="9.140625" customWidth="true"/>
+    <col min="6" max="6" width="10.140625" customWidth="true"/>
+    <col min="7" max="7" width="11.140625" customWidth="true"/>
     <col min="8" max="8" width="10.140625" customWidth="true"/>
     <col min="9" max="9" width="10.140625" customWidth="true"/>
-    <col min="10" max="10" width="11.140625" customWidth="true"/>
-    <col min="11" max="11" width="10.140625" customWidth="true"/>
-    <col min="12" max="12" width="11.85546875" customWidth="true"/>
-    <col min="13" max="13" width="10.140625" customWidth="true"/>
-    <col min="14" max="14" width="12.42578125" customWidth="true"/>
-    <col min="15" max="15" width="10.140625" customWidth="true"/>
+    <col min="10" max="10" width="10.140625" customWidth="true"/>
+    <col min="11" max="11" width="11.140625" customWidth="true"/>
+    <col min="12" max="12" width="10.140625" customWidth="true"/>
+    <col min="13" max="13" width="11.85546875" customWidth="true"/>
+    <col min="14" max="14" width="10.140625" customWidth="true"/>
+    <col min="15" max="15" width="12.42578125" customWidth="true"/>
     <col min="16" max="16" width="10.140625" customWidth="true"/>
-    <col min="17" max="17" width="9.140625" customWidth="true"/>
-    <col min="18" max="18" width="10.140625" customWidth="true"/>
-    <col min="19" max="19" width="9.140625" customWidth="true"/>
-    <col min="20" max="20" width="10.140625" customWidth="true"/>
+    <col min="17" max="17" width="10.140625" customWidth="true"/>
+    <col min="18" max="18" width="9.140625" customWidth="true"/>
+    <col min="19" max="19" width="10.140625" customWidth="true"/>
+    <col min="20" max="20" width="9.140625" customWidth="true"/>
     <col min="21" max="21" width="10.140625" customWidth="true"/>
     <col min="22" max="22" width="10.140625" customWidth="true"/>
     <col min="23" max="23" width="10.140625" customWidth="true"/>
-    <col min="24" max="24" width="11.140625" customWidth="true"/>
+    <col min="24" max="24" width="10.140625" customWidth="true"/>
+    <col min="25" max="25" width="11.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -272,73 +300,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>59</v>
+        <v>67</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2">
@@ -382,7 +413,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="0">
-        <v>80138770</v>
+        <v>0</v>
       </c>
       <c r="O2" s="0">
         <v>0</v>
@@ -400,7 +431,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="0">
-        <v>184138840</v>
+        <v>0</v>
       </c>
       <c r="U2" s="0">
         <v>0</v>
@@ -412,7 +443,10 @@
         <v>0</v>
       </c>
       <c r="X2" s="0">
-        <v>264277610</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +517,13 @@
         <v>0</v>
       </c>
       <c r="W3" s="0">
-        <v>136688420</v>
+        <v>0</v>
       </c>
       <c r="X3" s="0">
-        <v>136688420</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -530,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="0">
-        <v>1734940</v>
+        <v>0</v>
       </c>
       <c r="O4" s="0">
-        <v>0</v>
+        <v>80138770</v>
       </c>
       <c r="P4" s="0">
-        <v>114494470</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="0">
         <v>0</v>
@@ -551,16 +588,19 @@
         <v>0</v>
       </c>
       <c r="U4" s="0">
-        <v>0</v>
+        <v>184138840</v>
       </c>
       <c r="V4" s="0">
-        <v>20379080</v>
+        <v>0</v>
       </c>
       <c r="W4" s="0">
         <v>0</v>
       </c>
       <c r="X4" s="0">
-        <v>136608490</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="0">
+        <v>264277610</v>
       </c>
     </row>
     <row r="5">
@@ -610,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="P5" s="0">
-        <v>407343720</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="0">
         <v>0</v>
       </c>
       <c r="R5" s="0">
-        <v>116251000</v>
+        <v>0</v>
       </c>
       <c r="S5" s="0">
-        <v>79321710</v>
+        <v>0</v>
       </c>
       <c r="T5" s="0">
         <v>0</v>
@@ -628,13 +668,16 @@
         <v>0</v>
       </c>
       <c r="V5" s="0">
-        <v>493216130</v>
+        <v>0</v>
       </c>
       <c r="W5" s="0">
-        <v>563060320</v>
+        <v>0</v>
       </c>
       <c r="X5" s="0">
-        <v>1659192880</v>
+        <v>136688420</v>
+      </c>
+      <c r="Y5" s="0">
+        <v>136688420</v>
       </c>
     </row>
     <row r="6">
@@ -681,13 +724,13 @@
         <v>0</v>
       </c>
       <c r="O6" s="0">
-        <v>0</v>
+        <v>1734940</v>
       </c>
       <c r="P6" s="0">
         <v>0</v>
       </c>
       <c r="Q6" s="0">
-        <v>88250290</v>
+        <v>114494470</v>
       </c>
       <c r="R6" s="0">
         <v>0</v>
@@ -705,10 +748,13 @@
         <v>0</v>
       </c>
       <c r="W6" s="0">
-        <v>46297610</v>
+        <v>20379080</v>
       </c>
       <c r="X6" s="0">
-        <v>134547900</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="0">
+        <v>136608490</v>
       </c>
     </row>
     <row r="7">
@@ -755,34 +801,37 @@
         <v>0</v>
       </c>
       <c r="O7" s="0">
-        <v>2991440</v>
+        <v>0</v>
       </c>
       <c r="P7" s="0">
         <v>0</v>
       </c>
       <c r="Q7" s="0">
-        <v>0</v>
+        <v>407343720</v>
       </c>
       <c r="R7" s="0">
         <v>0</v>
       </c>
       <c r="S7" s="0">
-        <v>64090</v>
+        <v>116251000</v>
       </c>
       <c r="T7" s="0">
-        <v>0</v>
+        <v>79321710</v>
       </c>
       <c r="U7" s="0">
-        <v>198785630</v>
+        <v>0</v>
       </c>
       <c r="V7" s="0">
         <v>0</v>
       </c>
       <c r="W7" s="0">
-        <v>206145480</v>
+        <v>493216130</v>
       </c>
       <c r="X7" s="0">
-        <v>407986640</v>
+        <v>563060320</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>1659192880</v>
       </c>
     </row>
     <row r="8">
@@ -799,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>9575990</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0">
         <v>0</v>
@@ -811,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="0">
-        <v>81476930</v>
+        <v>0</v>
       </c>
       <c r="J8" s="0">
         <v>0</v>
@@ -856,7 +905,10 @@
         <v>0</v>
       </c>
       <c r="X8" s="0">
-        <v>91052920</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -903,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="0">
-        <v>388219300</v>
+        <v>0</v>
       </c>
       <c r="P9" s="0">
         <v>0</v>
@@ -912,25 +964,28 @@
         <v>0</v>
       </c>
       <c r="R9" s="0">
-        <v>0</v>
+        <v>88250290</v>
       </c>
       <c r="S9" s="0">
-        <v>6486760</v>
+        <v>0</v>
       </c>
       <c r="T9" s="0">
         <v>0</v>
       </c>
       <c r="U9" s="0">
-        <v>316870350</v>
+        <v>0</v>
       </c>
       <c r="V9" s="0">
         <v>0</v>
       </c>
       <c r="W9" s="0">
-        <v>71150530</v>
+        <v>0</v>
       </c>
       <c r="X9" s="0">
-        <v>782726940</v>
+        <v>46297610</v>
+      </c>
+      <c r="Y9" s="0">
+        <v>134547900</v>
       </c>
     </row>
     <row r="10">
@@ -950,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>267173000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="0">
         <v>0</v>
@@ -980,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="0">
-        <v>0</v>
+        <v>2991440</v>
       </c>
       <c r="Q10" s="0">
         <v>0</v>
@@ -992,19 +1047,22 @@
         <v>0</v>
       </c>
       <c r="T10" s="0">
-        <v>0</v>
+        <v>64090</v>
       </c>
       <c r="U10" s="0">
         <v>0</v>
       </c>
       <c r="V10" s="0">
-        <v>0</v>
+        <v>198785630</v>
       </c>
       <c r="W10" s="0">
         <v>0</v>
       </c>
       <c r="X10" s="0">
-        <v>267173000</v>
+        <v>206145480</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>407986640</v>
       </c>
     </row>
     <row r="11">
@@ -1021,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="0">
-        <v>119170560</v>
+        <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>240058000</v>
+        <v>9575990</v>
       </c>
       <c r="G11" s="0">
         <v>0</v>
@@ -1033,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="0">
-        <v>301683780</v>
+        <v>0</v>
       </c>
       <c r="J11" s="0">
-        <v>0</v>
+        <v>81476930</v>
       </c>
       <c r="K11" s="0">
         <v>0</v>
@@ -1078,7 +1136,10 @@
         <v>0</v>
       </c>
       <c r="X11" s="0">
-        <v>660912340</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>91052920</v>
       </c>
     </row>
     <row r="12">
@@ -1089,16 +1150,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="0">
-        <v>95467950</v>
+        <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>451945990</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>343283000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="0">
         <v>0</v>
@@ -1113,13 +1174,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="0">
-        <v>244990</v>
+        <v>0</v>
       </c>
       <c r="L12" s="0">
         <v>0</v>
       </c>
       <c r="M12" s="0">
-        <v>414131480</v>
+        <v>0</v>
       </c>
       <c r="N12" s="0">
         <v>0</v>
@@ -1128,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="0">
-        <v>0</v>
+        <v>388219300</v>
       </c>
       <c r="Q12" s="0">
         <v>0</v>
@@ -1140,19 +1201,22 @@
         <v>0</v>
       </c>
       <c r="T12" s="0">
-        <v>0</v>
+        <v>6486760</v>
       </c>
       <c r="U12" s="0">
         <v>0</v>
       </c>
       <c r="V12" s="0">
-        <v>0</v>
+        <v>316870350</v>
       </c>
       <c r="W12" s="0">
         <v>0</v>
       </c>
       <c r="X12" s="0">
-        <v>1305073410</v>
+        <v>71150530</v>
+      </c>
+      <c r="Y12" s="0">
+        <v>782726940</v>
       </c>
     </row>
     <row r="13">
@@ -1163,37 +1227,37 @@
         <v>0</v>
       </c>
       <c r="C13" s="0">
-        <v>274818570</v>
+        <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>203423790</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>343954000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>19049890</v>
+        <v>267173000</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>798800400</v>
+        <v>0</v>
       </c>
       <c r="J13" s="0">
         <v>0</v>
       </c>
       <c r="K13" s="0">
-        <v>259793340</v>
+        <v>0</v>
       </c>
       <c r="L13" s="0">
         <v>0</v>
       </c>
       <c r="M13" s="0">
-        <v>376765440</v>
+        <v>0</v>
       </c>
       <c r="N13" s="0">
         <v>0</v>
@@ -1226,7 +1290,10 @@
         <v>0</v>
       </c>
       <c r="X13" s="0">
-        <v>2276605430</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="0">
+        <v>267173000</v>
       </c>
     </row>
     <row r="14">
@@ -1246,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>0</v>
+        <v>119170560</v>
       </c>
       <c r="G14" s="0">
-        <v>263434950</v>
+        <v>240058000</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -1258,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <v>0</v>
+        <v>301683780</v>
       </c>
       <c r="K14" s="0">
-        <v>270930520</v>
+        <v>0</v>
       </c>
       <c r="L14" s="0">
         <v>0</v>
@@ -1300,7 +1367,10 @@
         <v>0</v>
       </c>
       <c r="X14" s="0">
-        <v>534365470</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="0">
+        <v>660912340</v>
       </c>
     </row>
     <row r="15">
@@ -1311,40 +1381,40 @@
         <v>0</v>
       </c>
       <c r="C15" s="0">
-        <v>0</v>
+        <v>95467950</v>
       </c>
       <c r="D15" s="0">
-        <v>1490724500</v>
+        <v>451945990</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>982816000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>79397300</v>
+        <v>343283000</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
       </c>
       <c r="I15" s="0">
-        <v>498184050</v>
+        <v>0</v>
       </c>
       <c r="J15" s="0">
         <v>0</v>
       </c>
       <c r="K15" s="0">
-        <v>113223700</v>
+        <v>0</v>
       </c>
       <c r="L15" s="0">
-        <v>0</v>
+        <v>244990</v>
       </c>
       <c r="M15" s="0">
         <v>0</v>
       </c>
       <c r="N15" s="0">
-        <v>0</v>
+        <v>414131480</v>
       </c>
       <c r="O15" s="0">
         <v>0</v>
@@ -1374,7 +1444,10 @@
         <v>0</v>
       </c>
       <c r="X15" s="0">
-        <v>3164345550</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="0">
+        <v>1305073410</v>
       </c>
     </row>
     <row r="16">
@@ -1385,40 +1458,40 @@
         <v>0</v>
       </c>
       <c r="C16" s="0">
-        <v>0</v>
+        <v>274818570</v>
       </c>
       <c r="D16" s="0">
-        <v>785200110</v>
+        <v>203423790</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <v>689589000</v>
+        <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>245871630</v>
+        <v>343954000</v>
       </c>
       <c r="H16" s="0">
-        <v>135572040</v>
+        <v>19049890</v>
       </c>
       <c r="I16" s="0">
-        <v>252920330</v>
+        <v>0</v>
       </c>
       <c r="J16" s="0">
-        <v>0</v>
+        <v>798800400</v>
       </c>
       <c r="K16" s="0">
-        <v>166284540</v>
+        <v>0</v>
       </c>
       <c r="L16" s="0">
-        <v>0</v>
+        <v>259793340</v>
       </c>
       <c r="M16" s="0">
-        <v>273502810</v>
+        <v>0</v>
       </c>
       <c r="N16" s="0">
-        <v>0</v>
+        <v>376765440</v>
       </c>
       <c r="O16" s="0">
         <v>0</v>
@@ -1448,7 +1521,10 @@
         <v>0</v>
       </c>
       <c r="X16" s="0">
-        <v>2548940460</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="0">
+        <v>2276605430</v>
       </c>
     </row>
     <row r="17">
@@ -1468,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <v>396062000</v>
+        <v>0</v>
       </c>
       <c r="G17" s="0">
         <v>0</v>
       </c>
       <c r="H17" s="0">
-        <v>60526990</v>
+        <v>263434950</v>
       </c>
       <c r="I17" s="0">
         <v>0</v>
@@ -1486,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="0">
-        <v>0</v>
+        <v>270930520</v>
       </c>
       <c r="M17" s="0">
         <v>0</v>
@@ -1522,7 +1598,10 @@
         <v>0</v>
       </c>
       <c r="X17" s="0">
-        <v>456588990</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="0">
+        <v>534365470</v>
       </c>
     </row>
     <row r="18">
@@ -1530,13 +1609,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>50885000</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0">
         <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>1490724500</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -1545,25 +1624,25 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>0</v>
+        <v>982816000</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>79397300</v>
       </c>
       <c r="I18" s="0">
         <v>0</v>
       </c>
       <c r="J18" s="0">
-        <v>2083460000</v>
+        <v>498184050</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>1657760</v>
+        <v>113223700</v>
       </c>
       <c r="M18" s="0">
-        <v>219276800</v>
+        <v>0</v>
       </c>
       <c r="N18" s="0">
         <v>0</v>
@@ -1596,7 +1675,10 @@
         <v>0</v>
       </c>
       <c r="X18" s="0">
-        <v>2355279560</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="0">
+        <v>3164345550</v>
       </c>
     </row>
     <row r="19">
@@ -1604,43 +1686,43 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>318054000</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0">
         <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>1749496100</v>
+        <v>785200110</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
       </c>
       <c r="F19" s="0">
-        <v>511209000</v>
+        <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>689589000</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>245871630</v>
       </c>
       <c r="I19" s="0">
-        <v>0</v>
+        <v>135572040</v>
       </c>
       <c r="J19" s="0">
-        <v>1400931000</v>
+        <v>252920330</v>
       </c>
       <c r="K19" s="0">
         <v>0</v>
       </c>
       <c r="L19" s="0">
-        <v>224270700</v>
+        <v>166284540</v>
       </c>
       <c r="M19" s="0">
-        <v>784789480</v>
+        <v>0</v>
       </c>
       <c r="N19" s="0">
-        <v>0</v>
+        <v>273502810</v>
       </c>
       <c r="O19" s="0">
         <v>0</v>
@@ -1655,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="0">
-        <v>-1440</v>
+        <v>0</v>
       </c>
       <c r="T19" s="0">
         <v>0</v>
@@ -1670,7 +1752,10 @@
         <v>0</v>
       </c>
       <c r="X19" s="0">
-        <v>4988748840</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="0">
+        <v>2548940460</v>
       </c>
     </row>
     <row r="20">
@@ -1678,13 +1763,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>47510000</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>43366270</v>
+        <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>543271120</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
         <v>0</v>
@@ -1702,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="0">
-        <v>1904410000</v>
+        <v>0</v>
       </c>
       <c r="K20" s="0">
         <v>0</v>
@@ -1711,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="0">
-        <v>932496660</v>
+        <v>0</v>
       </c>
       <c r="N20" s="0">
         <v>0</v>
@@ -1744,7 +1829,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="0">
-        <v>3471054050</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1752,7 +1840,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>12155000</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
@@ -1785,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="0">
-        <v>67838100</v>
+        <v>0</v>
       </c>
       <c r="N21" s="0">
         <v>0</v>
@@ -1818,7 +1906,10 @@
         <v>0</v>
       </c>
       <c r="X21" s="0">
-        <v>79993100</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1826,7 +1917,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>480886000</v>
+        <v>0</v>
       </c>
       <c r="C22" s="0">
         <v>0</v>
@@ -1838,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>1153648000</v>
+        <v>0</v>
       </c>
       <c r="G22" s="0">
-        <v>0</v>
+        <v>396062000</v>
       </c>
       <c r="H22" s="0">
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>0</v>
+        <v>60526990</v>
       </c>
       <c r="J22" s="0">
         <v>0</v>
@@ -1859,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="0">
-        <v>844495370</v>
+        <v>0</v>
       </c>
       <c r="N22" s="0">
         <v>0</v>
@@ -1892,7 +1983,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="0">
-        <v>2479029370</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="0">
+        <v>456588990</v>
       </c>
     </row>
     <row r="23">
@@ -1900,7 +1994,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>515047000</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0">
         <v>0</v>
@@ -1933,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="0">
-        <v>774062890</v>
+        <v>0</v>
       </c>
       <c r="N23" s="0">
         <v>0</v>
@@ -1966,7 +2060,10 @@
         <v>0</v>
       </c>
       <c r="X23" s="0">
-        <v>1289109890</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1986,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>530035000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
         <v>0</v>
@@ -2007,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="0">
-        <v>279205000</v>
+        <v>0</v>
       </c>
       <c r="N24" s="0">
         <v>0</v>
@@ -2028,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="0">
-        <v>0</v>
+        <v>-1440</v>
       </c>
       <c r="U24" s="0">
         <v>0</v>
@@ -2040,7 +2137,10 @@
         <v>0</v>
       </c>
       <c r="X24" s="0">
-        <v>809240000</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="0">
+        <v>-1440</v>
       </c>
     </row>
     <row r="25">
@@ -2060,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>112737000</v>
+        <v>0</v>
       </c>
       <c r="G25" s="0">
         <v>0</v>
@@ -2081,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="0">
-        <v>107953500</v>
+        <v>0</v>
       </c>
       <c r="N25" s="0">
         <v>0</v>
@@ -2114,7 +2214,10 @@
         <v>0</v>
       </c>
       <c r="X25" s="0">
-        <v>220690500</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2122,7 +2225,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>0</v>
+        <v>50885000</v>
       </c>
       <c r="C26" s="0">
         <v>0</v>
@@ -2131,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>0</v>
+        <v>19170130</v>
       </c>
       <c r="F26" s="0">
-        <v>403440000</v>
+        <v>0</v>
       </c>
       <c r="G26" s="0">
         <v>0</v>
@@ -2149,16 +2252,16 @@
         <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>0</v>
+        <v>2083460000</v>
       </c>
       <c r="L26" s="0">
         <v>0</v>
       </c>
       <c r="M26" s="0">
-        <v>401381540</v>
+        <v>1657760</v>
       </c>
       <c r="N26" s="0">
-        <v>0</v>
+        <v>219276800</v>
       </c>
       <c r="O26" s="0">
         <v>0</v>
@@ -2188,7 +2291,10 @@
         <v>0</v>
       </c>
       <c r="X26" s="0">
-        <v>804821540</v>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="0">
+        <v>2374449690</v>
       </c>
     </row>
     <row r="27">
@@ -2196,22 +2302,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>0</v>
+        <v>318054000</v>
       </c>
       <c r="C27" s="0">
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>0</v>
+        <v>1749496100</v>
       </c>
       <c r="E27" s="0">
-        <v>0</v>
+        <v>30594690</v>
       </c>
       <c r="F27" s="0">
-        <v>249179000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="0">
-        <v>0</v>
+        <v>511209000</v>
       </c>
       <c r="H27" s="0">
         <v>0</v>
@@ -2223,16 +2329,16 @@
         <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>0</v>
+        <v>1400931000</v>
       </c>
       <c r="L27" s="0">
         <v>0</v>
       </c>
       <c r="M27" s="0">
-        <v>181164800</v>
+        <v>224270700</v>
       </c>
       <c r="N27" s="0">
-        <v>0</v>
+        <v>784789480</v>
       </c>
       <c r="O27" s="0">
         <v>0</v>
@@ -2250,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="0">
-        <v>0</v>
+        <v>-1440</v>
       </c>
       <c r="U27" s="0">
         <v>0</v>
@@ -2262,7 +2368,10 @@
         <v>0</v>
       </c>
       <c r="X27" s="0">
-        <v>430343800</v>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="0">
+        <v>5019343530</v>
       </c>
     </row>
     <row r="28">
@@ -2270,25 +2379,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>0</v>
+        <v>47510000</v>
       </c>
       <c r="C28" s="0">
-        <v>0</v>
+        <v>43366270</v>
       </c>
       <c r="D28" s="0">
-        <v>0</v>
+        <v>543271120</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>137841000</v>
+        <v>0</v>
       </c>
       <c r="G28" s="0">
         <v>0</v>
       </c>
       <c r="H28" s="0">
-        <v>233436940</v>
+        <v>0</v>
       </c>
       <c r="I28" s="0">
         <v>0</v>
@@ -2297,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>0</v>
+        <v>1904410000</v>
       </c>
       <c r="L28" s="0">
         <v>0</v>
@@ -2306,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="0">
-        <v>0</v>
+        <v>932496660</v>
       </c>
       <c r="O28" s="0">
         <v>0</v>
@@ -2336,7 +2445,10 @@
         <v>0</v>
       </c>
       <c r="X28" s="0">
-        <v>371277940</v>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="0">
+        <v>3471054050</v>
       </c>
     </row>
     <row r="29">
@@ -2344,7 +2456,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>0</v>
+        <v>12155000</v>
       </c>
       <c r="C29" s="0">
         <v>0</v>
@@ -2356,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="0">
-        <v>414466000</v>
+        <v>0</v>
       </c>
       <c r="G29" s="0">
         <v>0</v>
@@ -2380,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="0">
-        <v>0</v>
+        <v>67838100</v>
       </c>
       <c r="O29" s="0">
         <v>0</v>
@@ -2410,7 +2522,10 @@
         <v>0</v>
       </c>
       <c r="X29" s="0">
-        <v>414466000</v>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="0">
+        <v>79993100</v>
       </c>
     </row>
     <row r="30">
@@ -2418,7 +2533,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>0</v>
+        <v>480886000</v>
       </c>
       <c r="C30" s="0">
         <v>0</v>
@@ -2430,13 +2545,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="0">
-        <v>523649000</v>
+        <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>0</v>
+        <v>1153648000</v>
       </c>
       <c r="H30" s="0">
-        <v>56773500</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0">
         <v>0</v>
@@ -2454,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="0">
-        <v>0</v>
+        <v>844495370</v>
       </c>
       <c r="O30" s="0">
         <v>0</v>
@@ -2484,7 +2599,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="0">
-        <v>580422500</v>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="0">
+        <v>2479029370</v>
       </c>
     </row>
     <row r="31">
@@ -2492,7 +2610,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>0</v>
+        <v>515047000</v>
       </c>
       <c r="C31" s="0">
         <v>0</v>
@@ -2504,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>599369000</v>
+        <v>0</v>
       </c>
       <c r="G31" s="0">
         <v>0</v>
@@ -2528,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="0">
-        <v>0</v>
+        <v>774062890</v>
       </c>
       <c r="O31" s="0">
         <v>0</v>
@@ -2558,7 +2676,10 @@
         <v>0</v>
       </c>
       <c r="X31" s="0">
-        <v>599369000</v>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="0">
+        <v>1289109890</v>
       </c>
     </row>
     <row r="32">
@@ -2572,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="0">
-        <v>483805410</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
         <v>0</v>
@@ -2581,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="0">
-        <v>0</v>
+        <v>530035000</v>
       </c>
       <c r="H32" s="0">
         <v>0</v>
@@ -2599,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="0">
-        <v>169669630</v>
+        <v>0</v>
       </c>
       <c r="N32" s="0">
-        <v>0</v>
+        <v>279205000</v>
       </c>
       <c r="O32" s="0">
         <v>0</v>
@@ -2632,7 +2753,10 @@
         <v>0</v>
       </c>
       <c r="X32" s="0">
-        <v>653475040</v>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="0">
+        <v>809240000</v>
       </c>
     </row>
     <row r="33">
@@ -2646,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="0">
-        <v>441231790</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0">
         <v>0</v>
@@ -2655,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>0</v>
+        <v>112737000</v>
       </c>
       <c r="H33" s="0">
         <v>0</v>
@@ -2673,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="0">
-        <v>774518620</v>
+        <v>0</v>
       </c>
       <c r="N33" s="0">
-        <v>0</v>
+        <v>107953500</v>
       </c>
       <c r="O33" s="0">
         <v>0</v>
@@ -2706,7 +2830,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="0">
-        <v>1215750410</v>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="0">
+        <v>220690500</v>
       </c>
     </row>
     <row r="34">
@@ -2729,10 +2856,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="0">
-        <v>0</v>
+        <v>403440000</v>
       </c>
       <c r="H34" s="0">
-        <v>36855160</v>
+        <v>0</v>
       </c>
       <c r="I34" s="0">
         <v>0</v>
@@ -2747,10 +2874,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="0">
-        <v>293105230</v>
+        <v>0</v>
       </c>
       <c r="N34" s="0">
-        <v>0</v>
+        <v>401381540</v>
       </c>
       <c r="O34" s="0">
         <v>0</v>
@@ -2780,7 +2907,10 @@
         <v>0</v>
       </c>
       <c r="X34" s="0">
-        <v>329960390</v>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="0">
+        <v>804821540</v>
       </c>
     </row>
     <row r="35">
@@ -2794,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="0">
-        <v>698045200</v>
+        <v>0</v>
       </c>
       <c r="E35" s="0">
         <v>0</v>
@@ -2803,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="0">
-        <v>0</v>
+        <v>249179000</v>
       </c>
       <c r="H35" s="0">
         <v>0</v>
@@ -2821,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="0">
-        <v>913604060</v>
+        <v>0</v>
       </c>
       <c r="N35" s="0">
-        <v>0</v>
+        <v>181164800</v>
       </c>
       <c r="O35" s="0">
         <v>0</v>
@@ -2854,7 +2984,10 @@
         <v>0</v>
       </c>
       <c r="X35" s="0">
-        <v>1611649260</v>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="0">
+        <v>430343800</v>
       </c>
     </row>
     <row r="36">
@@ -2868,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="0">
-        <v>349571140</v>
+        <v>0</v>
       </c>
       <c r="E36" s="0">
         <v>0</v>
@@ -2877,13 +3010,13 @@
         <v>0</v>
       </c>
       <c r="G36" s="0">
-        <v>0</v>
+        <v>137841000</v>
       </c>
       <c r="H36" s="0">
         <v>0</v>
       </c>
       <c r="I36" s="0">
-        <v>0</v>
+        <v>233436940</v>
       </c>
       <c r="J36" s="0">
         <v>0</v>
@@ -2895,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="0">
-        <v>343411130</v>
+        <v>0</v>
       </c>
       <c r="N36" s="0">
         <v>0</v>
@@ -2928,7 +3061,10 @@
         <v>0</v>
       </c>
       <c r="X36" s="0">
-        <v>692982270</v>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="0">
+        <v>371277940</v>
       </c>
     </row>
     <row r="37">
@@ -2936,73 +3072,692 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
+        <v>0</v>
+      </c>
+      <c r="C37" s="0">
+        <v>0</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0">
+        <v>0</v>
+      </c>
+      <c r="G37" s="0">
+        <v>414466000</v>
+      </c>
+      <c r="H37" s="0">
+        <v>0</v>
+      </c>
+      <c r="I37" s="0">
+        <v>0</v>
+      </c>
+      <c r="J37" s="0">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0</v>
+      </c>
+      <c r="N37" s="0">
+        <v>0</v>
+      </c>
+      <c r="O37" s="0">
+        <v>0</v>
+      </c>
+      <c r="P37" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="0">
+        <v>0</v>
+      </c>
+      <c r="R37" s="0">
+        <v>0</v>
+      </c>
+      <c r="S37" s="0">
+        <v>0</v>
+      </c>
+      <c r="T37" s="0">
+        <v>0</v>
+      </c>
+      <c r="U37" s="0">
+        <v>0</v>
+      </c>
+      <c r="V37" s="0">
+        <v>0</v>
+      </c>
+      <c r="W37" s="0">
+        <v>0</v>
+      </c>
+      <c r="X37" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="0">
+        <v>414466000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>0</v>
+      </c>
+      <c r="C38" s="0">
+        <v>0</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0">
+        <v>0</v>
+      </c>
+      <c r="F38" s="0">
+        <v>0</v>
+      </c>
+      <c r="G38" s="0">
+        <v>523649000</v>
+      </c>
+      <c r="H38" s="0">
+        <v>0</v>
+      </c>
+      <c r="I38" s="0">
+        <v>56773500</v>
+      </c>
+      <c r="J38" s="0">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0">
+        <v>0</v>
+      </c>
+      <c r="L38" s="0">
+        <v>0</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0</v>
+      </c>
+      <c r="N38" s="0">
+        <v>0</v>
+      </c>
+      <c r="O38" s="0">
+        <v>0</v>
+      </c>
+      <c r="P38" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="0">
+        <v>0</v>
+      </c>
+      <c r="R38" s="0">
+        <v>0</v>
+      </c>
+      <c r="S38" s="0">
+        <v>0</v>
+      </c>
+      <c r="T38" s="0">
+        <v>0</v>
+      </c>
+      <c r="U38" s="0">
+        <v>0</v>
+      </c>
+      <c r="V38" s="0">
+        <v>0</v>
+      </c>
+      <c r="W38" s="0">
+        <v>0</v>
+      </c>
+      <c r="X38" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="0">
+        <v>580422500</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>0</v>
+      </c>
+      <c r="C39" s="0">
+        <v>0</v>
+      </c>
+      <c r="D39" s="0">
+        <v>0</v>
+      </c>
+      <c r="E39" s="0">
+        <v>0</v>
+      </c>
+      <c r="F39" s="0">
+        <v>0</v>
+      </c>
+      <c r="G39" s="0">
+        <v>599369000</v>
+      </c>
+      <c r="H39" s="0">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0">
+        <v>0</v>
+      </c>
+      <c r="J39" s="0">
+        <v>0</v>
+      </c>
+      <c r="K39" s="0">
+        <v>0</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0</v>
+      </c>
+      <c r="N39" s="0">
+        <v>0</v>
+      </c>
+      <c r="O39" s="0">
+        <v>0</v>
+      </c>
+      <c r="P39" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="0">
+        <v>0</v>
+      </c>
+      <c r="R39" s="0">
+        <v>0</v>
+      </c>
+      <c r="S39" s="0">
+        <v>0</v>
+      </c>
+      <c r="T39" s="0">
+        <v>0</v>
+      </c>
+      <c r="U39" s="0">
+        <v>0</v>
+      </c>
+      <c r="V39" s="0">
+        <v>0</v>
+      </c>
+      <c r="W39" s="0">
+        <v>0</v>
+      </c>
+      <c r="X39" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="0">
+        <v>599369000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0">
+        <v>0</v>
+      </c>
+      <c r="C40" s="0">
+        <v>0</v>
+      </c>
+      <c r="D40" s="0">
+        <v>483805410</v>
+      </c>
+      <c r="E40" s="0">
+        <v>0</v>
+      </c>
+      <c r="F40" s="0">
+        <v>0</v>
+      </c>
+      <c r="G40" s="0">
+        <v>0</v>
+      </c>
+      <c r="H40" s="0">
+        <v>0</v>
+      </c>
+      <c r="I40" s="0">
+        <v>0</v>
+      </c>
+      <c r="J40" s="0">
+        <v>0</v>
+      </c>
+      <c r="K40" s="0">
+        <v>0</v>
+      </c>
+      <c r="L40" s="0">
+        <v>0</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0</v>
+      </c>
+      <c r="N40" s="0">
+        <v>169669630</v>
+      </c>
+      <c r="O40" s="0">
+        <v>0</v>
+      </c>
+      <c r="P40" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="0">
+        <v>0</v>
+      </c>
+      <c r="R40" s="0">
+        <v>0</v>
+      </c>
+      <c r="S40" s="0">
+        <v>0</v>
+      </c>
+      <c r="T40" s="0">
+        <v>0</v>
+      </c>
+      <c r="U40" s="0">
+        <v>0</v>
+      </c>
+      <c r="V40" s="0">
+        <v>0</v>
+      </c>
+      <c r="W40" s="0">
+        <v>0</v>
+      </c>
+      <c r="X40" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="0">
+        <v>653475040</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0">
+        <v>0</v>
+      </c>
+      <c r="C41" s="0">
+        <v>0</v>
+      </c>
+      <c r="D41" s="0">
+        <v>441231790</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0">
+        <v>0</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" s="0">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0">
+        <v>0</v>
+      </c>
+      <c r="J41" s="0">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0">
+        <v>0</v>
+      </c>
+      <c r="L41" s="0">
+        <v>0</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0</v>
+      </c>
+      <c r="N41" s="0">
+        <v>774518620</v>
+      </c>
+      <c r="O41" s="0">
+        <v>0</v>
+      </c>
+      <c r="P41" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="0">
+        <v>0</v>
+      </c>
+      <c r="R41" s="0">
+        <v>0</v>
+      </c>
+      <c r="S41" s="0">
+        <v>0</v>
+      </c>
+      <c r="T41" s="0">
+        <v>0</v>
+      </c>
+      <c r="U41" s="0">
+        <v>0</v>
+      </c>
+      <c r="V41" s="0">
+        <v>0</v>
+      </c>
+      <c r="W41" s="0">
+        <v>0</v>
+      </c>
+      <c r="X41" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="0">
+        <v>1215750410</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="0">
+        <v>0</v>
+      </c>
+      <c r="C42" s="0">
+        <v>0</v>
+      </c>
+      <c r="D42" s="0">
+        <v>0</v>
+      </c>
+      <c r="E42" s="0">
+        <v>0</v>
+      </c>
+      <c r="F42" s="0">
+        <v>0</v>
+      </c>
+      <c r="G42" s="0">
+        <v>0</v>
+      </c>
+      <c r="H42" s="0">
+        <v>0</v>
+      </c>
+      <c r="I42" s="0">
+        <v>36855160</v>
+      </c>
+      <c r="J42" s="0">
+        <v>0</v>
+      </c>
+      <c r="K42" s="0">
+        <v>0</v>
+      </c>
+      <c r="L42" s="0">
+        <v>0</v>
+      </c>
+      <c r="M42" s="0">
+        <v>0</v>
+      </c>
+      <c r="N42" s="0">
+        <v>293105230</v>
+      </c>
+      <c r="O42" s="0">
+        <v>0</v>
+      </c>
+      <c r="P42" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="0">
+        <v>0</v>
+      </c>
+      <c r="R42" s="0">
+        <v>0</v>
+      </c>
+      <c r="S42" s="0">
+        <v>0</v>
+      </c>
+      <c r="T42" s="0">
+        <v>0</v>
+      </c>
+      <c r="U42" s="0">
+        <v>0</v>
+      </c>
+      <c r="V42" s="0">
+        <v>0</v>
+      </c>
+      <c r="W42" s="0">
+        <v>0</v>
+      </c>
+      <c r="X42" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="0">
+        <v>329960390</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="0">
+        <v>0</v>
+      </c>
+      <c r="C43" s="0">
+        <v>0</v>
+      </c>
+      <c r="D43" s="0">
+        <v>698045200</v>
+      </c>
+      <c r="E43" s="0">
+        <v>0</v>
+      </c>
+      <c r="F43" s="0">
+        <v>0</v>
+      </c>
+      <c r="G43" s="0">
+        <v>0</v>
+      </c>
+      <c r="H43" s="0">
+        <v>0</v>
+      </c>
+      <c r="I43" s="0">
+        <v>0</v>
+      </c>
+      <c r="J43" s="0">
+        <v>0</v>
+      </c>
+      <c r="K43" s="0">
+        <v>0</v>
+      </c>
+      <c r="L43" s="0">
+        <v>0</v>
+      </c>
+      <c r="M43" s="0">
+        <v>0</v>
+      </c>
+      <c r="N43" s="0">
+        <v>913604060</v>
+      </c>
+      <c r="O43" s="0">
+        <v>0</v>
+      </c>
+      <c r="P43" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="0">
+        <v>0</v>
+      </c>
+      <c r="R43" s="0">
+        <v>0</v>
+      </c>
+      <c r="S43" s="0">
+        <v>0</v>
+      </c>
+      <c r="T43" s="0">
+        <v>0</v>
+      </c>
+      <c r="U43" s="0">
+        <v>0</v>
+      </c>
+      <c r="V43" s="0">
+        <v>0</v>
+      </c>
+      <c r="W43" s="0">
+        <v>0</v>
+      </c>
+      <c r="X43" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="0">
+        <v>1611649260</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="0">
+        <v>0</v>
+      </c>
+      <c r="C44" s="0">
+        <v>0</v>
+      </c>
+      <c r="D44" s="0">
+        <v>349571140</v>
+      </c>
+      <c r="E44" s="0">
+        <v>0</v>
+      </c>
+      <c r="F44" s="0">
+        <v>0</v>
+      </c>
+      <c r="G44" s="0">
+        <v>0</v>
+      </c>
+      <c r="H44" s="0">
+        <v>0</v>
+      </c>
+      <c r="I44" s="0">
+        <v>0</v>
+      </c>
+      <c r="J44" s="0">
+        <v>0</v>
+      </c>
+      <c r="K44" s="0">
+        <v>0</v>
+      </c>
+      <c r="L44" s="0">
+        <v>0</v>
+      </c>
+      <c r="M44" s="0">
+        <v>0</v>
+      </c>
+      <c r="N44" s="0">
+        <v>343411130</v>
+      </c>
+      <c r="O44" s="0">
+        <v>0</v>
+      </c>
+      <c r="P44" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="0">
+        <v>0</v>
+      </c>
+      <c r="R44" s="0">
+        <v>0</v>
+      </c>
+      <c r="S44" s="0">
+        <v>0</v>
+      </c>
+      <c r="T44" s="0">
+        <v>0</v>
+      </c>
+      <c r="U44" s="0">
+        <v>0</v>
+      </c>
+      <c r="V44" s="0">
+        <v>0</v>
+      </c>
+      <c r="W44" s="0">
+        <v>0</v>
+      </c>
+      <c r="X44" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="0">
+        <v>692982270</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="0">
         <v>1424537000</v>
       </c>
-      <c r="C37" s="0">
+      <c r="C45" s="0">
         <v>413652790</v>
       </c>
-      <c r="D37" s="0">
+      <c r="D45" s="0">
         <v>7196715150</v>
       </c>
-      <c r="E37" s="0">
+      <c r="E45" s="0">
+        <v>49764820</v>
+      </c>
+      <c r="F45" s="0">
         <v>128746550</v>
       </c>
-      <c r="F37" s="0">
+      <c r="G45" s="0">
         <v>7898508000</v>
       </c>
-      <c r="G37" s="0">
+      <c r="H45" s="0">
         <v>607753770</v>
       </c>
-      <c r="H37" s="0">
+      <c r="I45" s="0">
         <v>523164630</v>
       </c>
-      <c r="I37" s="0">
+      <c r="J45" s="0">
         <v>1933065490</v>
       </c>
-      <c r="J37" s="0">
+      <c r="K45" s="0">
         <v>5388801000</v>
       </c>
-      <c r="K37" s="0">
+      <c r="L45" s="0">
         <v>810477090</v>
       </c>
-      <c r="L37" s="0">
+      <c r="M45" s="0">
         <v>225928460</v>
       </c>
-      <c r="M37" s="0">
+      <c r="N45" s="0">
         <v>8151372540</v>
       </c>
-      <c r="N37" s="0">
+      <c r="O45" s="0">
         <v>81873710</v>
       </c>
-      <c r="O37" s="0">
+      <c r="P45" s="0">
         <v>391210740</v>
       </c>
-      <c r="P37" s="0">
+      <c r="Q45" s="0">
         <v>521838190</v>
       </c>
-      <c r="Q37" s="0">
+      <c r="R45" s="0">
         <v>88250290</v>
       </c>
-      <c r="R37" s="0">
+      <c r="S45" s="0">
         <v>116251000</v>
       </c>
-      <c r="S37" s="0">
-        <v>85871120</v>
-      </c>
-      <c r="T37" s="0">
+      <c r="T45" s="0">
+        <v>85869680</v>
+      </c>
+      <c r="U45" s="0">
         <v>184138840</v>
       </c>
-      <c r="U37" s="0">
+      <c r="V45" s="0">
         <v>515655980</v>
       </c>
-      <c r="V37" s="0">
+      <c r="W45" s="0">
         <v>513595210</v>
       </c>
-      <c r="W37" s="0">
+      <c r="X45" s="0">
         <v>1023342360</v>
       </c>
-      <c r="X37" s="0">
-        <v>38224749910</v>
+      <c r="Y45" s="0">
+        <v>38274513290</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aircraft Operating Costs Tables/2025/Crew_Costs_by_Aircraft_and_Airline_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aircraft Operating Costs Tables/2025/Crew_Costs_by_Aircraft_and_Airline_2025.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="76" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -36,6 +36,15 @@
     <t>E175</t>
   </si>
   <si>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
+  </si>
+  <si>
     <t>Q400</t>
   </si>
   <si>
@@ -217,6 +226,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -265,7 +286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -293,6 +314,10 @@
     <col min="23" max="23" width="10.140625" customWidth="true"/>
     <col min="24" max="24" width="10.140625" customWidth="true"/>
     <col min="25" max="25" width="11.140625" customWidth="true"/>
+    <col min="26" max="26" width="11.140625" customWidth="true"/>
+    <col min="27" max="27" width="10.140625" customWidth="true"/>
+    <col min="28" max="28" width="11.140625" customWidth="true"/>
+    <col min="29" max="29" width="11.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -300,76 +325,88 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Y1" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -448,6 +485,18 @@
       <c r="Y2" s="0">
         <v>0</v>
       </c>
+      <c r="Z2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -525,6 +574,18 @@
       <c r="Y3" s="0">
         <v>0</v>
       </c>
+      <c r="Z3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -600,6 +661,18 @@
         <v>0</v>
       </c>
       <c r="Y4" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>264277610</v>
+      </c>
+      <c r="AC4" s="0">
         <v>264277610</v>
       </c>
     </row>
@@ -677,6 +750,18 @@
         <v>136688420</v>
       </c>
       <c r="Y5" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>136688420</v>
+      </c>
+      <c r="AC5" s="0">
         <v>136688420</v>
       </c>
     </row>
@@ -754,6 +839,18 @@
         <v>0</v>
       </c>
       <c r="Y6" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>136608490</v>
+      </c>
+      <c r="AC6" s="0">
         <v>136608490</v>
       </c>
     </row>
@@ -831,6 +928,18 @@
         <v>563060320</v>
       </c>
       <c r="Y7" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>1659192880</v>
+      </c>
+      <c r="AC7" s="0">
         <v>1659192880</v>
       </c>
     </row>
@@ -910,6 +1019,18 @@
       <c r="Y8" s="0">
         <v>0</v>
       </c>
+      <c r="Z8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -964,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="0">
-        <v>88250290</v>
+        <v>0</v>
       </c>
       <c r="S9" s="0">
         <v>0</v>
@@ -982,10 +1103,22 @@
         <v>0</v>
       </c>
       <c r="X9" s="0">
-        <v>46297610</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="0">
-        <v>134547900</v>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1035,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="0">
-        <v>2991440</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="0">
         <v>0</v>
@@ -1047,22 +1180,34 @@
         <v>0</v>
       </c>
       <c r="T10" s="0">
-        <v>64090</v>
+        <v>0</v>
       </c>
       <c r="U10" s="0">
         <v>0</v>
       </c>
       <c r="V10" s="0">
-        <v>198785630</v>
+        <v>0</v>
       </c>
       <c r="W10" s="0">
         <v>0</v>
       </c>
       <c r="X10" s="0">
-        <v>206145480</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="0">
-        <v>407986640</v>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1082,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>9575990</v>
+        <v>0</v>
       </c>
       <c r="G11" s="0">
         <v>0</v>
@@ -1094,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="0">
-        <v>81476930</v>
+        <v>0</v>
       </c>
       <c r="K11" s="0">
         <v>0</v>
@@ -1139,7 +1284,19 @@
         <v>0</v>
       </c>
       <c r="Y11" s="0">
-        <v>91052920</v>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1189,34 +1346,46 @@
         <v>0</v>
       </c>
       <c r="P12" s="0">
-        <v>388219300</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="0">
         <v>0</v>
       </c>
       <c r="R12" s="0">
-        <v>0</v>
+        <v>88250290</v>
       </c>
       <c r="S12" s="0">
         <v>0</v>
       </c>
       <c r="T12" s="0">
-        <v>6486760</v>
+        <v>0</v>
       </c>
       <c r="U12" s="0">
         <v>0</v>
       </c>
       <c r="V12" s="0">
-        <v>316870350</v>
+        <v>0</v>
       </c>
       <c r="W12" s="0">
         <v>0</v>
       </c>
       <c r="X12" s="0">
-        <v>71150530</v>
+        <v>46297610</v>
       </c>
       <c r="Y12" s="0">
-        <v>782726940</v>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="0">
+        <v>134547900</v>
+      </c>
+      <c r="AC12" s="0">
+        <v>134547900</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>267173000</v>
+        <v>0</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -1266,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="0">
-        <v>0</v>
+        <v>2991440</v>
       </c>
       <c r="Q13" s="0">
         <v>0</v>
@@ -1278,22 +1447,34 @@
         <v>0</v>
       </c>
       <c r="T13" s="0">
-        <v>0</v>
+        <v>64090</v>
       </c>
       <c r="U13" s="0">
         <v>0</v>
       </c>
       <c r="V13" s="0">
-        <v>0</v>
+        <v>198785630</v>
       </c>
       <c r="W13" s="0">
         <v>0</v>
       </c>
       <c r="X13" s="0">
-        <v>0</v>
+        <v>206145480</v>
       </c>
       <c r="Y13" s="0">
-        <v>267173000</v>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="0">
+        <v>407986640</v>
+      </c>
+      <c r="AC13" s="0">
+        <v>407986640</v>
       </c>
     </row>
     <row r="14">
@@ -1313,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>119170560</v>
+        <v>9575990</v>
       </c>
       <c r="G14" s="0">
-        <v>240058000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -1325,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <v>301683780</v>
+        <v>81476930</v>
       </c>
       <c r="K14" s="0">
         <v>0</v>
@@ -1370,7 +1551,19 @@
         <v>0</v>
       </c>
       <c r="Y14" s="0">
-        <v>660912340</v>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>91052920</v>
+      </c>
+      <c r="AA14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="0">
+        <v>91052920</v>
       </c>
     </row>
     <row r="15">
@@ -1381,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="0">
-        <v>95467950</v>
+        <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>451945990</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -1393,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>343283000</v>
+        <v>0</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -1408,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="L15" s="0">
-        <v>244990</v>
+        <v>0</v>
       </c>
       <c r="M15" s="0">
         <v>0</v>
       </c>
       <c r="N15" s="0">
-        <v>414131480</v>
+        <v>0</v>
       </c>
       <c r="O15" s="0">
         <v>0</v>
       </c>
       <c r="P15" s="0">
-        <v>0</v>
+        <v>388219300</v>
       </c>
       <c r="Q15" s="0">
         <v>0</v>
@@ -1432,22 +1625,34 @@
         <v>0</v>
       </c>
       <c r="T15" s="0">
-        <v>0</v>
+        <v>6486760</v>
       </c>
       <c r="U15" s="0">
         <v>0</v>
       </c>
       <c r="V15" s="0">
-        <v>0</v>
+        <v>316870350</v>
       </c>
       <c r="W15" s="0">
         <v>0</v>
       </c>
       <c r="X15" s="0">
-        <v>0</v>
+        <v>71150530</v>
       </c>
       <c r="Y15" s="0">
-        <v>1305073410</v>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="0">
+        <v>782726940</v>
+      </c>
+      <c r="AC15" s="0">
+        <v>782726940</v>
       </c>
     </row>
     <row r="16">
@@ -1458,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="0">
-        <v>274818570</v>
+        <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>203423790</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -1470,28 +1675,28 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>343954000</v>
+        <v>267173000</v>
       </c>
       <c r="H16" s="0">
-        <v>19049890</v>
+        <v>0</v>
       </c>
       <c r="I16" s="0">
         <v>0</v>
       </c>
       <c r="J16" s="0">
-        <v>798800400</v>
+        <v>0</v>
       </c>
       <c r="K16" s="0">
         <v>0</v>
       </c>
       <c r="L16" s="0">
-        <v>259793340</v>
+        <v>0</v>
       </c>
       <c r="M16" s="0">
         <v>0</v>
       </c>
       <c r="N16" s="0">
-        <v>376765440</v>
+        <v>0</v>
       </c>
       <c r="O16" s="0">
         <v>0</v>
@@ -1524,7 +1729,19 @@
         <v>0</v>
       </c>
       <c r="Y16" s="0">
-        <v>2276605430</v>
+        <v>267173000</v>
+      </c>
+      <c r="Z16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="0">
+        <v>267173000</v>
       </c>
     </row>
     <row r="17">
@@ -1544,25 +1761,25 @@
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <v>0</v>
+        <v>119170560</v>
       </c>
       <c r="G17" s="0">
-        <v>0</v>
+        <v>240058000</v>
       </c>
       <c r="H17" s="0">
-        <v>263434950</v>
+        <v>0</v>
       </c>
       <c r="I17" s="0">
         <v>0</v>
       </c>
       <c r="J17" s="0">
-        <v>0</v>
+        <v>301683780</v>
       </c>
       <c r="K17" s="0">
         <v>0</v>
       </c>
       <c r="L17" s="0">
-        <v>270930520</v>
+        <v>0</v>
       </c>
       <c r="M17" s="0">
         <v>0</v>
@@ -1601,7 +1818,19 @@
         <v>0</v>
       </c>
       <c r="Y17" s="0">
-        <v>534365470</v>
+        <v>240058000</v>
+      </c>
+      <c r="Z17" s="0">
+        <v>420854340</v>
+      </c>
+      <c r="AA17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="0">
+        <v>660912340</v>
       </c>
     </row>
     <row r="18">
@@ -1612,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0</v>
+        <v>95467950</v>
       </c>
       <c r="D18" s="0">
-        <v>1490724500</v>
+        <v>451945990</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -1624,28 +1853,28 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>982816000</v>
+        <v>343283000</v>
       </c>
       <c r="H18" s="0">
-        <v>79397300</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0">
         <v>0</v>
       </c>
       <c r="J18" s="0">
-        <v>498184050</v>
+        <v>0</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>113223700</v>
+        <v>244990</v>
       </c>
       <c r="M18" s="0">
         <v>0</v>
       </c>
       <c r="N18" s="0">
-        <v>0</v>
+        <v>414131480</v>
       </c>
       <c r="O18" s="0">
         <v>0</v>
@@ -1678,7 +1907,19 @@
         <v>0</v>
       </c>
       <c r="Y18" s="0">
-        <v>3164345550</v>
+        <v>1209360470</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="0">
+        <v>95712940</v>
+      </c>
+      <c r="AB18" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="0">
+        <v>1305073410</v>
       </c>
     </row>
     <row r="19">
@@ -1689,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="0">
-        <v>0</v>
+        <v>274818570</v>
       </c>
       <c r="D19" s="0">
-        <v>785200110</v>
+        <v>203423790</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -1701,28 +1942,28 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>689589000</v>
+        <v>343954000</v>
       </c>
       <c r="H19" s="0">
-        <v>245871630</v>
+        <v>19049890</v>
       </c>
       <c r="I19" s="0">
-        <v>135572040</v>
+        <v>0</v>
       </c>
       <c r="J19" s="0">
-        <v>252920330</v>
+        <v>798800400</v>
       </c>
       <c r="K19" s="0">
         <v>0</v>
       </c>
       <c r="L19" s="0">
-        <v>166284540</v>
+        <v>259793340</v>
       </c>
       <c r="M19" s="0">
         <v>0</v>
       </c>
       <c r="N19" s="0">
-        <v>273502810</v>
+        <v>376765440</v>
       </c>
       <c r="O19" s="0">
         <v>0</v>
@@ -1755,7 +1996,19 @@
         <v>0</v>
       </c>
       <c r="Y19" s="0">
-        <v>2548940460</v>
+        <v>924143230</v>
+      </c>
+      <c r="Z19" s="0">
+        <v>798800400</v>
+      </c>
+      <c r="AA19" s="0">
+        <v>553661800</v>
+      </c>
+      <c r="AB19" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="0">
+        <v>2276605430</v>
       </c>
     </row>
     <row r="20">
@@ -1781,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>263434950</v>
       </c>
       <c r="I20" s="0">
         <v>0</v>
@@ -1793,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>0</v>
+        <v>270930520</v>
       </c>
       <c r="M20" s="0">
         <v>0</v>
@@ -1833,6 +2086,18 @@
       </c>
       <c r="Y20" s="0">
         <v>0</v>
+      </c>
+      <c r="Z20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>534365470</v>
+      </c>
+      <c r="AB20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="0">
+        <v>534365470</v>
       </c>
     </row>
     <row r="21">
@@ -1846,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>1490724500</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1855,22 +2120,22 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>0</v>
+        <v>982816000</v>
       </c>
       <c r="H21" s="0">
-        <v>0</v>
+        <v>79397300</v>
       </c>
       <c r="I21" s="0">
         <v>0</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>498184050</v>
       </c>
       <c r="K21" s="0">
         <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>0</v>
+        <v>113223700</v>
       </c>
       <c r="M21" s="0">
         <v>0</v>
@@ -1909,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Y21" s="0">
-        <v>0</v>
+        <v>2473540500</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>498184050</v>
+      </c>
+      <c r="AA21" s="0">
+        <v>192621000</v>
+      </c>
+      <c r="AB21" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="0">
+        <v>3164345550</v>
       </c>
     </row>
     <row r="22">
@@ -1923,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>785200110</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1932,28 +2209,28 @@
         <v>0</v>
       </c>
       <c r="G22" s="0">
-        <v>396062000</v>
+        <v>689589000</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>245871630</v>
       </c>
       <c r="I22" s="0">
-        <v>60526990</v>
+        <v>135572040</v>
       </c>
       <c r="J22" s="0">
-        <v>0</v>
+        <v>252920330</v>
       </c>
       <c r="K22" s="0">
         <v>0</v>
       </c>
       <c r="L22" s="0">
-        <v>0</v>
+        <v>166284540</v>
       </c>
       <c r="M22" s="0">
         <v>0</v>
       </c>
       <c r="N22" s="0">
-        <v>0</v>
+        <v>273502810</v>
       </c>
       <c r="O22" s="0">
         <v>0</v>
@@ -1986,7 +2263,19 @@
         <v>0</v>
       </c>
       <c r="Y22" s="0">
-        <v>456588990</v>
+        <v>1748291920</v>
+      </c>
+      <c r="Z22" s="0">
+        <v>388492370</v>
+      </c>
+      <c r="AA22" s="0">
+        <v>412156170</v>
+      </c>
+      <c r="AB22" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="0">
+        <v>2548940460</v>
       </c>
     </row>
     <row r="23">
@@ -2065,6 +2354,18 @@
       <c r="Y23" s="0">
         <v>0</v>
       </c>
+      <c r="Z23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
@@ -2125,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="0">
-        <v>-1440</v>
+        <v>0</v>
       </c>
       <c r="U24" s="0">
         <v>0</v>
@@ -2140,7 +2441,19 @@
         <v>0</v>
       </c>
       <c r="Y24" s="0">
-        <v>-1440</v>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2163,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>396062000</v>
       </c>
       <c r="H25" s="0">
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0</v>
+        <v>60526990</v>
       </c>
       <c r="J25" s="0">
         <v>0</v>
@@ -2217,7 +2530,19 @@
         <v>0</v>
       </c>
       <c r="Y25" s="0">
-        <v>0</v>
+        <v>396062000</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>60526990</v>
+      </c>
+      <c r="AA25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="0">
+        <v>456588990</v>
       </c>
     </row>
     <row r="26">
@@ -2225,7 +2550,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>50885000</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
         <v>0</v>
@@ -2234,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>19170130</v>
+        <v>0</v>
       </c>
       <c r="F26" s="0">
         <v>0</v>
@@ -2252,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>2083460000</v>
+        <v>0</v>
       </c>
       <c r="L26" s="0">
         <v>0</v>
       </c>
       <c r="M26" s="0">
-        <v>1657760</v>
+        <v>0</v>
       </c>
       <c r="N26" s="0">
-        <v>219276800</v>
+        <v>0</v>
       </c>
       <c r="O26" s="0">
         <v>0</v>
@@ -2294,7 +2619,19 @@
         <v>0</v>
       </c>
       <c r="Y26" s="0">
-        <v>2374449690</v>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2302,22 +2639,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>318054000</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0">
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>1749496100</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>30594690</v>
+        <v>0</v>
       </c>
       <c r="F27" s="0">
         <v>0</v>
       </c>
       <c r="G27" s="0">
-        <v>511209000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
         <v>0</v>
@@ -2329,16 +2666,16 @@
         <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>1400931000</v>
+        <v>0</v>
       </c>
       <c r="L27" s="0">
         <v>0</v>
       </c>
       <c r="M27" s="0">
-        <v>224270700</v>
+        <v>0</v>
       </c>
       <c r="N27" s="0">
-        <v>784789480</v>
+        <v>0</v>
       </c>
       <c r="O27" s="0">
         <v>0</v>
@@ -2371,7 +2708,19 @@
         <v>0</v>
       </c>
       <c r="Y27" s="0">
-        <v>5019343530</v>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="0">
+        <v>-1440</v>
+      </c>
+      <c r="AC27" s="0">
+        <v>-1440</v>
       </c>
     </row>
     <row r="28">
@@ -2379,13 +2728,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>47510000</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0">
-        <v>43366270</v>
+        <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>543271120</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -2406,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>1904410000</v>
+        <v>0</v>
       </c>
       <c r="L28" s="0">
         <v>0</v>
@@ -2415,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="0">
-        <v>932496660</v>
+        <v>0</v>
       </c>
       <c r="O28" s="0">
         <v>0</v>
@@ -2448,7 +2797,19 @@
         <v>0</v>
       </c>
       <c r="Y28" s="0">
-        <v>3471054050</v>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2456,7 +2817,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>12155000</v>
+        <v>50885000</v>
       </c>
       <c r="C29" s="0">
         <v>0</v>
@@ -2465,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="0">
-        <v>0</v>
+        <v>19170130</v>
       </c>
       <c r="F29" s="0">
         <v>0</v>
@@ -2483,16 +2844,16 @@
         <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>0</v>
+        <v>2083460000</v>
       </c>
       <c r="L29" s="0">
         <v>0</v>
       </c>
       <c r="M29" s="0">
-        <v>0</v>
+        <v>1657760</v>
       </c>
       <c r="N29" s="0">
-        <v>67838100</v>
+        <v>219276800</v>
       </c>
       <c r="O29" s="0">
         <v>0</v>
@@ -2525,7 +2886,19 @@
         <v>0</v>
       </c>
       <c r="Y29" s="0">
-        <v>79993100</v>
+        <v>219276800</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>2134345000</v>
+      </c>
+      <c r="AA29" s="0">
+        <v>20827890</v>
+      </c>
+      <c r="AB29" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="0">
+        <v>2374449690</v>
       </c>
     </row>
     <row r="30">
@@ -2533,22 +2906,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>480886000</v>
+        <v>318054000</v>
       </c>
       <c r="C30" s="0">
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>0</v>
+        <v>1749496100</v>
       </c>
       <c r="E30" s="0">
-        <v>0</v>
+        <v>30594690</v>
       </c>
       <c r="F30" s="0">
         <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>1153648000</v>
+        <v>511209000</v>
       </c>
       <c r="H30" s="0">
         <v>0</v>
@@ -2560,16 +2933,16 @@
         <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>0</v>
+        <v>1400931000</v>
       </c>
       <c r="L30" s="0">
         <v>0</v>
       </c>
       <c r="M30" s="0">
-        <v>0</v>
+        <v>224270700</v>
       </c>
       <c r="N30" s="0">
-        <v>844495370</v>
+        <v>784789480</v>
       </c>
       <c r="O30" s="0">
         <v>0</v>
@@ -2587,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="0">
-        <v>0</v>
+        <v>-1440</v>
       </c>
       <c r="U30" s="0">
         <v>0</v>
@@ -2602,7 +2975,19 @@
         <v>0</v>
       </c>
       <c r="Y30" s="0">
-        <v>2479029370</v>
+        <v>3045494580</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>1718985000</v>
+      </c>
+      <c r="AA30" s="0">
+        <v>254865390</v>
+      </c>
+      <c r="AB30" s="0">
+        <v>-1440</v>
+      </c>
+      <c r="AC30" s="0">
+        <v>5019343530</v>
       </c>
     </row>
     <row r="31">
@@ -2610,13 +2995,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>515047000</v>
+        <v>47510000</v>
       </c>
       <c r="C31" s="0">
-        <v>0</v>
+        <v>43366270</v>
       </c>
       <c r="D31" s="0">
-        <v>0</v>
+        <v>543271120</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
@@ -2637,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>0</v>
+        <v>1904410000</v>
       </c>
       <c r="L31" s="0">
         <v>0</v>
@@ -2646,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="0">
-        <v>774062890</v>
+        <v>932496660</v>
       </c>
       <c r="O31" s="0">
         <v>0</v>
@@ -2679,7 +3064,19 @@
         <v>0</v>
       </c>
       <c r="Y31" s="0">
-        <v>1289109890</v>
+        <v>1475767780</v>
+      </c>
+      <c r="Z31" s="0">
+        <v>1951920000</v>
+      </c>
+      <c r="AA31" s="0">
+        <v>43366270</v>
+      </c>
+      <c r="AB31" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="0">
+        <v>3471054050</v>
       </c>
     </row>
     <row r="32">
@@ -2687,7 +3084,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0</v>
+        <v>12155000</v>
       </c>
       <c r="C32" s="0">
         <v>0</v>
@@ -2702,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="0">
-        <v>530035000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="0">
         <v>0</v>
@@ -2723,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="0">
-        <v>279205000</v>
+        <v>67838100</v>
       </c>
       <c r="O32" s="0">
         <v>0</v>
@@ -2756,7 +3153,19 @@
         <v>0</v>
       </c>
       <c r="Y32" s="0">
-        <v>809240000</v>
+        <v>67838100</v>
+      </c>
+      <c r="Z32" s="0">
+        <v>12155000</v>
+      </c>
+      <c r="AA32" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="0">
+        <v>79993100</v>
       </c>
     </row>
     <row r="33">
@@ -2764,7 +3173,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>0</v>
+        <v>480886000</v>
       </c>
       <c r="C33" s="0">
         <v>0</v>
@@ -2779,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>112737000</v>
+        <v>1153648000</v>
       </c>
       <c r="H33" s="0">
         <v>0</v>
@@ -2800,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="0">
-        <v>107953500</v>
+        <v>844495370</v>
       </c>
       <c r="O33" s="0">
         <v>0</v>
@@ -2833,7 +3242,19 @@
         <v>0</v>
       </c>
       <c r="Y33" s="0">
-        <v>220690500</v>
+        <v>1998143370</v>
+      </c>
+      <c r="Z33" s="0">
+        <v>480886000</v>
+      </c>
+      <c r="AA33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="0">
+        <v>2479029370</v>
       </c>
     </row>
     <row r="34">
@@ -2841,7 +3262,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>0</v>
+        <v>515047000</v>
       </c>
       <c r="C34" s="0">
         <v>0</v>
@@ -2856,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="0">
-        <v>403440000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="0">
         <v>0</v>
@@ -2877,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="0">
-        <v>401381540</v>
+        <v>774062890</v>
       </c>
       <c r="O34" s="0">
         <v>0</v>
@@ -2910,7 +3331,19 @@
         <v>0</v>
       </c>
       <c r="Y34" s="0">
-        <v>804821540</v>
+        <v>774062890</v>
+      </c>
+      <c r="Z34" s="0">
+        <v>515047000</v>
+      </c>
+      <c r="AA34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="0">
+        <v>1289109890</v>
       </c>
     </row>
     <row r="35">
@@ -2933,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="0">
-        <v>249179000</v>
+        <v>530035000</v>
       </c>
       <c r="H35" s="0">
         <v>0</v>
@@ -2954,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="0">
-        <v>181164800</v>
+        <v>279205000</v>
       </c>
       <c r="O35" s="0">
         <v>0</v>
@@ -2987,7 +3420,19 @@
         <v>0</v>
       </c>
       <c r="Y35" s="0">
-        <v>430343800</v>
+        <v>809240000</v>
+      </c>
+      <c r="Z35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="0">
+        <v>809240000</v>
       </c>
     </row>
     <row r="36">
@@ -3010,13 +3455,13 @@
         <v>0</v>
       </c>
       <c r="G36" s="0">
-        <v>137841000</v>
+        <v>112737000</v>
       </c>
       <c r="H36" s="0">
         <v>0</v>
       </c>
       <c r="I36" s="0">
-        <v>233436940</v>
+        <v>0</v>
       </c>
       <c r="J36" s="0">
         <v>0</v>
@@ -3031,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="0">
-        <v>0</v>
+        <v>107953500</v>
       </c>
       <c r="O36" s="0">
         <v>0</v>
@@ -3064,7 +3509,19 @@
         <v>0</v>
       </c>
       <c r="Y36" s="0">
-        <v>371277940</v>
+        <v>220690500</v>
+      </c>
+      <c r="Z36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="0">
+        <v>220690500</v>
       </c>
     </row>
     <row r="37">
@@ -3087,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="0">
-        <v>414466000</v>
+        <v>403440000</v>
       </c>
       <c r="H37" s="0">
         <v>0</v>
@@ -3108,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="0">
-        <v>0</v>
+        <v>401381540</v>
       </c>
       <c r="O37" s="0">
         <v>0</v>
@@ -3141,7 +3598,19 @@
         <v>0</v>
       </c>
       <c r="Y37" s="0">
-        <v>414466000</v>
+        <v>804821540</v>
+      </c>
+      <c r="Z37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="0">
+        <v>804821540</v>
       </c>
     </row>
     <row r="38">
@@ -3164,13 +3633,13 @@
         <v>0</v>
       </c>
       <c r="G38" s="0">
-        <v>523649000</v>
+        <v>249179000</v>
       </c>
       <c r="H38" s="0">
         <v>0</v>
       </c>
       <c r="I38" s="0">
-        <v>56773500</v>
+        <v>0</v>
       </c>
       <c r="J38" s="0">
         <v>0</v>
@@ -3185,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="0">
-        <v>0</v>
+        <v>181164800</v>
       </c>
       <c r="O38" s="0">
         <v>0</v>
@@ -3218,7 +3687,19 @@
         <v>0</v>
       </c>
       <c r="Y38" s="0">
-        <v>580422500</v>
+        <v>430343800</v>
+      </c>
+      <c r="Z38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="0">
+        <v>430343800</v>
       </c>
     </row>
     <row r="39">
@@ -3241,13 +3722,13 @@
         <v>0</v>
       </c>
       <c r="G39" s="0">
-        <v>599369000</v>
+        <v>137841000</v>
       </c>
       <c r="H39" s="0">
         <v>0</v>
       </c>
       <c r="I39" s="0">
-        <v>0</v>
+        <v>233436940</v>
       </c>
       <c r="J39" s="0">
         <v>0</v>
@@ -3295,7 +3776,19 @@
         <v>0</v>
       </c>
       <c r="Y39" s="0">
-        <v>599369000</v>
+        <v>137841000</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>233436940</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="0">
+        <v>371277940</v>
       </c>
     </row>
     <row r="40">
@@ -3309,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="0">
-        <v>483805410</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0">
         <v>0</v>
@@ -3318,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="0">
-        <v>0</v>
+        <v>414466000</v>
       </c>
       <c r="H40" s="0">
         <v>0</v>
@@ -3339,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="0">
-        <v>169669630</v>
+        <v>0</v>
       </c>
       <c r="O40" s="0">
         <v>0</v>
@@ -3372,7 +3865,19 @@
         <v>0</v>
       </c>
       <c r="Y40" s="0">
-        <v>653475040</v>
+        <v>414466000</v>
+      </c>
+      <c r="Z40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="0">
+        <v>414466000</v>
       </c>
     </row>
     <row r="41">
@@ -3386,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="0">
-        <v>441231790</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0">
         <v>0</v>
@@ -3395,13 +3900,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="0">
-        <v>0</v>
+        <v>523649000</v>
       </c>
       <c r="H41" s="0">
         <v>0</v>
       </c>
       <c r="I41" s="0">
-        <v>0</v>
+        <v>56773500</v>
       </c>
       <c r="J41" s="0">
         <v>0</v>
@@ -3416,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="0">
-        <v>774518620</v>
+        <v>0</v>
       </c>
       <c r="O41" s="0">
         <v>0</v>
@@ -3449,7 +3954,19 @@
         <v>0</v>
       </c>
       <c r="Y41" s="0">
-        <v>1215750410</v>
+        <v>523649000</v>
+      </c>
+      <c r="Z41" s="0">
+        <v>56773500</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="0">
+        <v>580422500</v>
       </c>
     </row>
     <row r="42">
@@ -3472,13 +3989,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="0">
-        <v>0</v>
+        <v>599369000</v>
       </c>
       <c r="H42" s="0">
         <v>0</v>
       </c>
       <c r="I42" s="0">
-        <v>36855160</v>
+        <v>0</v>
       </c>
       <c r="J42" s="0">
         <v>0</v>
@@ -3493,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="0">
-        <v>293105230</v>
+        <v>0</v>
       </c>
       <c r="O42" s="0">
         <v>0</v>
@@ -3526,7 +4043,19 @@
         <v>0</v>
       </c>
       <c r="Y42" s="0">
-        <v>329960390</v>
+        <v>599369000</v>
+      </c>
+      <c r="Z42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="0">
+        <v>599369000</v>
       </c>
     </row>
     <row r="43">
@@ -3540,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="0">
-        <v>698045200</v>
+        <v>483805410</v>
       </c>
       <c r="E43" s="0">
         <v>0</v>
@@ -3570,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="0">
-        <v>913604060</v>
+        <v>169669630</v>
       </c>
       <c r="O43" s="0">
         <v>0</v>
@@ -3603,7 +4132,19 @@
         <v>0</v>
       </c>
       <c r="Y43" s="0">
-        <v>1611649260</v>
+        <v>653475040</v>
+      </c>
+      <c r="Z43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="0">
+        <v>653475040</v>
       </c>
     </row>
     <row r="44">
@@ -3617,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="0">
-        <v>349571140</v>
+        <v>441231790</v>
       </c>
       <c r="E44" s="0">
         <v>0</v>
@@ -3647,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="0">
-        <v>343411130</v>
+        <v>774518620</v>
       </c>
       <c r="O44" s="0">
         <v>0</v>
@@ -3680,7 +4221,19 @@
         <v>0</v>
       </c>
       <c r="Y44" s="0">
-        <v>692982270</v>
+        <v>1215750410</v>
+      </c>
+      <c r="Z44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="0">
+        <v>1215750410</v>
       </c>
     </row>
     <row r="45">
@@ -3688,75 +4241,354 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
+        <v>0</v>
+      </c>
+      <c r="C45" s="0">
+        <v>0</v>
+      </c>
+      <c r="D45" s="0">
+        <v>0</v>
+      </c>
+      <c r="E45" s="0">
+        <v>0</v>
+      </c>
+      <c r="F45" s="0">
+        <v>0</v>
+      </c>
+      <c r="G45" s="0">
+        <v>0</v>
+      </c>
+      <c r="H45" s="0">
+        <v>0</v>
+      </c>
+      <c r="I45" s="0">
+        <v>36855160</v>
+      </c>
+      <c r="J45" s="0">
+        <v>0</v>
+      </c>
+      <c r="K45" s="0">
+        <v>0</v>
+      </c>
+      <c r="L45" s="0">
+        <v>0</v>
+      </c>
+      <c r="M45" s="0">
+        <v>0</v>
+      </c>
+      <c r="N45" s="0">
+        <v>293105230</v>
+      </c>
+      <c r="O45" s="0">
+        <v>0</v>
+      </c>
+      <c r="P45" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="0">
+        <v>0</v>
+      </c>
+      <c r="R45" s="0">
+        <v>0</v>
+      </c>
+      <c r="S45" s="0">
+        <v>0</v>
+      </c>
+      <c r="T45" s="0">
+        <v>0</v>
+      </c>
+      <c r="U45" s="0">
+        <v>0</v>
+      </c>
+      <c r="V45" s="0">
+        <v>0</v>
+      </c>
+      <c r="W45" s="0">
+        <v>0</v>
+      </c>
+      <c r="X45" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="0">
+        <v>293105230</v>
+      </c>
+      <c r="Z45" s="0">
+        <v>36855160</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="0">
+        <v>329960390</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="0">
+        <v>0</v>
+      </c>
+      <c r="C46" s="0">
+        <v>0</v>
+      </c>
+      <c r="D46" s="0">
+        <v>698045200</v>
+      </c>
+      <c r="E46" s="0">
+        <v>0</v>
+      </c>
+      <c r="F46" s="0">
+        <v>0</v>
+      </c>
+      <c r="G46" s="0">
+        <v>0</v>
+      </c>
+      <c r="H46" s="0">
+        <v>0</v>
+      </c>
+      <c r="I46" s="0">
+        <v>0</v>
+      </c>
+      <c r="J46" s="0">
+        <v>0</v>
+      </c>
+      <c r="K46" s="0">
+        <v>0</v>
+      </c>
+      <c r="L46" s="0">
+        <v>0</v>
+      </c>
+      <c r="M46" s="0">
+        <v>0</v>
+      </c>
+      <c r="N46" s="0">
+        <v>913604060</v>
+      </c>
+      <c r="O46" s="0">
+        <v>0</v>
+      </c>
+      <c r="P46" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="0">
+        <v>0</v>
+      </c>
+      <c r="R46" s="0">
+        <v>0</v>
+      </c>
+      <c r="S46" s="0">
+        <v>0</v>
+      </c>
+      <c r="T46" s="0">
+        <v>0</v>
+      </c>
+      <c r="U46" s="0">
+        <v>0</v>
+      </c>
+      <c r="V46" s="0">
+        <v>0</v>
+      </c>
+      <c r="W46" s="0">
+        <v>0</v>
+      </c>
+      <c r="X46" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="0">
+        <v>1611649260</v>
+      </c>
+      <c r="Z46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="0">
+        <v>1611649260</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="0">
+        <v>0</v>
+      </c>
+      <c r="C47" s="0">
+        <v>0</v>
+      </c>
+      <c r="D47" s="0">
+        <v>349571140</v>
+      </c>
+      <c r="E47" s="0">
+        <v>0</v>
+      </c>
+      <c r="F47" s="0">
+        <v>0</v>
+      </c>
+      <c r="G47" s="0">
+        <v>0</v>
+      </c>
+      <c r="H47" s="0">
+        <v>0</v>
+      </c>
+      <c r="I47" s="0">
+        <v>0</v>
+      </c>
+      <c r="J47" s="0">
+        <v>0</v>
+      </c>
+      <c r="K47" s="0">
+        <v>0</v>
+      </c>
+      <c r="L47" s="0">
+        <v>0</v>
+      </c>
+      <c r="M47" s="0">
+        <v>0</v>
+      </c>
+      <c r="N47" s="0">
+        <v>343411130</v>
+      </c>
+      <c r="O47" s="0">
+        <v>0</v>
+      </c>
+      <c r="P47" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="0">
+        <v>0</v>
+      </c>
+      <c r="R47" s="0">
+        <v>0</v>
+      </c>
+      <c r="S47" s="0">
+        <v>0</v>
+      </c>
+      <c r="T47" s="0">
+        <v>0</v>
+      </c>
+      <c r="U47" s="0">
+        <v>0</v>
+      </c>
+      <c r="V47" s="0">
+        <v>0</v>
+      </c>
+      <c r="W47" s="0">
+        <v>0</v>
+      </c>
+      <c r="X47" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="0">
+        <v>692982270</v>
+      </c>
+      <c r="Z47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="0">
+        <v>692982270</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="0">
         <v>1424537000</v>
       </c>
-      <c r="C45" s="0">
+      <c r="C48" s="0">
         <v>413652790</v>
       </c>
-      <c r="D45" s="0">
+      <c r="D48" s="0">
         <v>7196715150</v>
       </c>
-      <c r="E45" s="0">
+      <c r="E48" s="0">
         <v>49764820</v>
       </c>
-      <c r="F45" s="0">
+      <c r="F48" s="0">
         <v>128746550</v>
       </c>
-      <c r="G45" s="0">
+      <c r="G48" s="0">
         <v>7898508000</v>
       </c>
-      <c r="H45" s="0">
+      <c r="H48" s="0">
         <v>607753770</v>
       </c>
-      <c r="I45" s="0">
+      <c r="I48" s="0">
         <v>523164630</v>
       </c>
-      <c r="J45" s="0">
+      <c r="J48" s="0">
         <v>1933065490</v>
       </c>
-      <c r="K45" s="0">
+      <c r="K48" s="0">
         <v>5388801000</v>
       </c>
-      <c r="L45" s="0">
+      <c r="L48" s="0">
         <v>810477090</v>
       </c>
-      <c r="M45" s="0">
+      <c r="M48" s="0">
         <v>225928460</v>
       </c>
-      <c r="N45" s="0">
+      <c r="N48" s="0">
         <v>8151372540</v>
       </c>
-      <c r="O45" s="0">
+      <c r="O48" s="0">
         <v>81873710</v>
       </c>
-      <c r="P45" s="0">
+      <c r="P48" s="0">
         <v>391210740</v>
       </c>
-      <c r="Q45" s="0">
+      <c r="Q48" s="0">
         <v>521838190</v>
       </c>
-      <c r="R45" s="0">
+      <c r="R48" s="0">
         <v>88250290</v>
       </c>
-      <c r="S45" s="0">
+      <c r="S48" s="0">
         <v>116251000</v>
       </c>
-      <c r="T45" s="0">
+      <c r="T48" s="0">
         <v>85869680</v>
       </c>
-      <c r="U45" s="0">
+      <c r="U48" s="0">
         <v>184138840</v>
       </c>
-      <c r="V45" s="0">
+      <c r="V48" s="0">
         <v>515655980</v>
       </c>
-      <c r="W45" s="0">
+      <c r="W48" s="0">
         <v>513595210</v>
       </c>
-      <c r="X45" s="0">
+      <c r="X48" s="0">
         <v>1023342360</v>
       </c>
-      <c r="Y45" s="0">
+      <c r="Y48" s="0">
+        <v>23246595690</v>
+      </c>
+      <c r="Z48" s="0">
+        <v>9398314670</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>2107576930</v>
+      </c>
+      <c r="AB48" s="0">
+        <v>3522026000</v>
+      </c>
+      <c r="AC48" s="0">
         <v>38274513290</v>
       </c>
     </row>
